--- a/docs/별첨D_화면설계서.xlsx
+++ b/docs/별첨D_화면설계서.xlsx
@@ -211,6 +211,66 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>48</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9334500" cy="5524500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>44</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9334500" cy="4429125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -782,7 +842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1476,13 +1536,26 @@
       <c r="E45" s="4" t="n"/>
       <c r="F45" s="4" t="n"/>
     </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>7. 화면 예시 (샘플 목업 — 문서 기준 재현)</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="n"/>
+      <c r="C47" s="4" t="n"/>
+      <c r="D47" s="4" t="n"/>
+      <c r="E47" s="4" t="n"/>
+      <c r="F47" s="4" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A33:F33"/>
     <mergeCell ref="B44:F44"/>
     <mergeCell ref="B7:F7"/>
+    <mergeCell ref="A47:F47"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
@@ -1494,6 +1567,7 @@
     <mergeCell ref="A43:F43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1503,7 +1577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2038,8 +2112,20 @@
       <c r="E41" s="4" t="n"/>
       <c r="F41" s="4" t="n"/>
     </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>7. 화면 예시 (샘플 목업 — 문서 기준 재현)</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n"/>
+      <c r="C43" s="4" t="n"/>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="4" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A16:F16"/>
@@ -2055,7 +2141,9 @@
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A43:F43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/docs/별첨D_화면설계서.xlsx
+++ b/docs/별첨D_화면설계서.xlsx
@@ -222,7 +222,7 @@
       <row>48</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9334500" cy="5524500"/>
+    <ext cx="9334500" cy="5457825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>미사용 시 외부 호출 차단 (active_yn / status_code)</t>
+          <t>라디오 버튼(사용/미사용). 미사용 시 외부 호출 차단 (active_yn / status_code)</t>
         </is>
       </c>
     </row>

--- a/docs/별첨D_화면설계서.xlsx
+++ b/docs/별첨D_화면설계서.xlsx
@@ -219,7 +219,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>48</row>
+      <row>49</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9334500" cy="5457825"/>
@@ -842,15 +842,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1018,7 +1018,7 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>3. 입력 필드 명세 (§8.3)</t>
+          <t>3. 입력 필드 명세 (§8.3) — 저장 위치 및 저장 시 유효성 체크</t>
         </is>
       </c>
       <c r="B14" s="4" t="n"/>
@@ -1040,12 +1040,22 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
+          <t>컨트롤</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>저장 위치 (테이블.컬럼)</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>저장 시 유효성 체크</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
           <t>예시</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>검증 기준 / 비고</t>
         </is>
       </c>
     </row>
@@ -1062,12 +1072,22 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
+          <t>입력(신규)/읽기전용(수정)</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>BS_SERVICE.service_id</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>정규식 ^[A-Z0-9]+(\.[A-Z0-9]+)+$ (대문자·숫자+점) · 중복 금지(existsById) · Handler.serviceId()와 일치</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
           <t>IFRS17.CLOSING.STATUS</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>대문자·점(.) 구분, 중복 금지, Handler ID와 일치 (BS_SERVICE.service_id)</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1104,22 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>BS_SERVICE.service_name</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>필수 · 100자 이내</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
           <t>결산 진행상태 조회</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>100자 이내 (BS_SERVICE.service_name)</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1136,22 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>BS_SERVICE.service_description</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>필수(§8.3) · varchar(300)</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
           <t>결산 단계별 처리상태를 조회한다</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>업무 목적과 결과 설명 (BS_SERVICE.service_description)</t>
         </is>
       </c>
     </row>
@@ -1128,19 +1168,29 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>BS_SERVICE_VERSION.version</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>필수 · 동일 Service ID 내 중복 금지</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
           <t>1.0</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>동일 Service ID 내 중복 금지 (BS_SERVICE_VERSION.version)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Spring Bean명</t>
+          <t>Spring Bean</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -1150,12 +1200,22 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>BS_SERVICE_VERSION.implementation_bean</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>필수 · Bean 존재 · BusinessServiceHandler 구현 · Handler.serviceId()=Service ID</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
           <t>closingStatusBusinessService</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>WAS에 존재 + BusinessServiceHandler 구현 (implementation_bean)</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1232,22 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
+          <t>텍스트영역</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>BS_SERVICE_VERSION.request_schema</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>JSON 형식·필수값 정의(§8.3)</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
           <t>{ closingMonth, closingType }</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>JSON 형식·필수값 정의 (bs_service_version.request_schema)</t>
         </is>
       </c>
     </row>
@@ -1194,19 +1264,29 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
+          <t>텍스트영역</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>BS_SERVICE_VERSION.response_schema</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>JSON 형식·필드 설명(§8.3)</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
           <t>{ stage, status, startTime, endTime }</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>JSON 형식·필드 설명 (bs_service_version.response_schema)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>허용 역할 → 필요 권한</t>
+          <t>필요 권한</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -1216,12 +1296,22 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>CLSGM001:inqy</t>
+          <t>텍스트(멀티)</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>[확정] 화면ID:액션 형식. 화면ID=[A-Z]{4}M[0-9]{3}, 액션=inqy/sv/cnfr/aprl/prt. 외부 권한API 화면권한과 AND 비교 (BS_SERVICE_ROLE.role_code)</t>
+          <t>BS_SERVICE_ROLE.role_code (행 단위 N개)</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>최소 1개 · 형식 화면ID:액션 = [A-Z]{4}M[0-9]{3}:(inqy|sv|cnfr|aprl|prt)</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>ICCOM123:inqy</t>
         </is>
       </c>
     </row>
@@ -1238,283 +1328,293 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>사용 / 미사용</t>
+          <t>라디오(사용/미사용)</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>라디오 버튼(사용/미사용). 미사용 시 외부 호출 차단 (active_yn / status_code)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+          <t>BS_SERVICE.active_yn + BS_SERVICE_VERSION.status_code</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>사용→active_yn=Y &amp; status_code=ACTIVE / 미사용→N &amp; INACTIVE · '사용' 저장 시 Bean 재검증</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>유효성 근거</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>저장 검증은 ServiceSpecService(create/update·validateCommon·validateBean, CON-ACC-01)에서 수행. '필요 권한' 형식검증(화면ID:액션)은 확정 규약으로 코드 반영 예정.</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>4. 버튼 / 기능</t>
         </is>
       </c>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="n"/>
-      <c r="F26" s="4" t="n"/>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>버튼</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>동작</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>처리</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>조회</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>목록 검색</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>검색어(서비스ID/서비스명)로 서비스 목록 조회</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>등록 시작</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>우측 폼 초기화, 신규 서비스 명세 입력</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>저장</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>등록/수정 확정</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>Bean 존재·Interface 구현·Service ID/버전 일치 검증 후 저장. 사용=저장 시 Registry 갱신→외부 호출 허용</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>취소</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>입력 취소</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>편집 내용 폐기</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>5. 처리 로직 — 서비스 등록·외부 공개 흐름 (§8.4)</t>
         </is>
       </c>
-      <c r="B33" s="4" t="n"/>
-      <c r="C33" s="4" t="n"/>
-      <c r="D33" s="4" t="n"/>
-      <c r="E33" s="4" t="n"/>
-      <c r="F33" s="4" t="n"/>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>순서</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>처리</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>주체</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>BusinessServiceHandler 구현 클래스 작성·테스트</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>개발자</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>Java 클래스를 IFRS17 WAS에 배포</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>DB-INC</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>관리콘솔에서 서비스 명세 신규 등록</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>운영자</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>Bean 존재·Interface 구현·Service ID/버전 일치 검증</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>시스템</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>서비스 Test 화면에서 요청·응답 확인</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>운영자</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>사용 여부 '사용' 저장 → Registry 갱신, 외부 호출 허용</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>시스템</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>사용 여부 '미사용' 변경 → 즉시 신규 호출 차단</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>시스템</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>6. 연계</t>
         </is>
       </c>
-      <c r="B43" s="4" t="n"/>
-      <c r="C43" s="4" t="n"/>
-      <c r="D43" s="4" t="n"/>
-      <c r="E43" s="4" t="n"/>
-      <c r="F43" s="4" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>연계 테이블</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>BS_SERVICE, BS_SERVICE_VERSION, BS_SERVICE_ROLE (+ BS_CHANGE_HISTORY 변경이력)</t>
-        </is>
-      </c>
+      <c r="B44" s="4" t="n"/>
       <c r="C44" s="4" t="n"/>
       <c r="D44" s="4" t="n"/>
       <c r="E44" s="4" t="n"/>
@@ -1523,12 +1623,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>검증(CON-ACC-01)</t>
+          <t>연계 테이블</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Bean 미등록/Interface 미구현/ServiceId 불일치 시 저장·사용전환 차단</t>
+          <t>BS_SERVICE, BS_SERVICE_VERSION, BS_SERVICE_ROLE (+ BS_CHANGE_HISTORY 변경이력)</t>
         </is>
       </c>
       <c r="C45" s="4" t="n"/>
@@ -1536,35 +1636,52 @@
       <c r="E45" s="4" t="n"/>
       <c r="F45" s="4" t="n"/>
     </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>검증(CON-ACC-01)</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Bean 미등록/Interface 미구현/ServiceId 불일치 시 저장·사용전환 차단</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="4" t="n"/>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="n"/>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>7. 화면 예시 (샘플 목업 — 문서 기준 재현)</t>
         </is>
       </c>
-      <c r="B47" s="4" t="n"/>
-      <c r="C47" s="4" t="n"/>
-      <c r="D47" s="4" t="n"/>
-      <c r="E47" s="4" t="n"/>
-      <c r="F47" s="4" t="n"/>
+      <c r="B48" s="4" t="n"/>
+      <c r="C48" s="4" t="n"/>
+      <c r="D48" s="4" t="n"/>
+      <c r="E48" s="4" t="n"/>
+      <c r="F48" s="4" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="B44:F44"/>
     <mergeCell ref="B7:F7"/>
-    <mergeCell ref="A47:F47"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A44:F44"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B25:F25"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A27:F27"/>
     <mergeCell ref="B45:F45"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="A48:F48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/docs/별첨D_화면설계서.xlsx
+++ b/docs/별첨D_화면설계서.xlsx
@@ -249,7 +249,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>44</row>
+      <row>45</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9334500" cy="4429125"/>
@@ -1694,15 +1694,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1904,7 +1904,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>3. 입력 항목</t>
+          <t>3. 입력 항목 — 요청 매핑 및 유효성 체크</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -1926,12 +1926,22 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
+          <t>컨트롤</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>요청 매핑 (Controller/DTO)</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>유효성 체크</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
           <t>예시</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>비고</t>
         </is>
       </c>
     </row>
@@ -1948,12 +1958,22 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
+          <t>목록 선택</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Path {serviceId} → BusinessServiceController.execute</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>사용/미사용 선택 가능하나 미배포·Bean 불일치는 실행 불가(§8.6)</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
           <t>IFRS17.CLOSING.STATUS</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>목록에서 선택</t>
         </is>
       </c>
     </row>
@@ -1970,12 +1990,22 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>StandardRequest.serviceVersion</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>미입력 시 최신 ACTIVE 버전 자동 선택</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
           <t>1.0</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>미입력 시 최신 ACTIVE 버전 자동 선택</t>
         </is>
       </c>
     </row>
@@ -1992,19 +2022,29 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
+          <t>텍스트영역</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>StandardRequest.parameters</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>등록된 요청 명세 기준 형식·필수값 검증 → Handler.validate()(§8.6)</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
           <t>{ "parameters": { "closingYearMonth": "2026-06" } }</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>등록된 요청 명세 기준 형식·필수값 검증</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>4. 출력 항목 (§8.6)</t>
+          <t>4. 출력 항목 — 표시 및 감사로그 저장 위치 (§8.6)</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
@@ -2024,6 +2064,11 @@
           <t>설명</t>
         </is>
       </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>산출 / 저장 위치 (테이블.컬럼)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -2036,6 +2081,11 @@
           <t>응답 HTTP 상태코드 (예: 200, 400, 403, 500)</t>
         </is>
       </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>ResponseEntity status + BS_CALL_LOG.http_status</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -2048,6 +2098,11 @@
           <t>표준 Response 형식(JSON)</t>
         </is>
       </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>StandardResponse (결과 원문 미저장 · parameter_hash만 기록)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -2060,6 +2115,11 @@
           <t>실패 시 표준 오류코드(부록A: BS-VAL-001 등)와 메시지</t>
         </is>
       </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>StandardResponse.error + BS_CALL_LOG.error_code / error_id</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -2072,126 +2132,131 @@
           <t>서버 처리 소요시간(ms)</t>
         </is>
       </c>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>StandardResponse.elapsedMs + BS_CALL_LOG.elapsed_ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>감사 기록</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>모든 Test 실행은 운영 호출과 동일 경로로 BS_CALL_LOG에 감사 기록됨(request_id·status_code·elapsed_ms 등, §8.6)</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>5. 처리 기준 (§8.6)</t>
         </is>
       </c>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="4" t="n"/>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="n"/>
-      <c r="F29" s="4" t="n"/>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>기준</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>목록에서 사용/미사용 서비스 선택 가능하나, 미배포·Bean 불일치 서비스는 실행 불가</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>Request JSON은 등록된 요청 명세에 따라 형식·필수값 검증</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>Test 실행은 운영 호출과 동일 경로(Controller·Dispatcher·권한검사·Handler·감사로그) 사용</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>화면에 HTTP 상태·표준 Response JSON·오류코드/메시지·처리시간 표시</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>Phase 1 운영환경 Test는 READ 서비스만 허용</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>민감 데이터는 일반 호출과 동일 기준으로 마스킹</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>6. 연계</t>
         </is>
       </c>
-      <c r="B38" s="4" t="n"/>
-      <c r="C38" s="4" t="n"/>
-      <c r="D38" s="4" t="n"/>
-      <c r="E38" s="4" t="n"/>
-      <c r="F38" s="4" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>공통 Endpoint</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>POST /api/business-services/v1/{serviceId}:execute</t>
-        </is>
-      </c>
+      <c r="B39" s="4" t="n"/>
       <c r="C39" s="4" t="n"/>
       <c r="D39" s="4" t="n"/>
       <c r="E39" s="4" t="n"/>
@@ -2200,12 +2265,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>필수 Header</t>
+          <t>공통 Endpoint</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>X-Client-ID(Y), Authorization(Y), Content-Type: application/json (§5.2)</t>
+          <t>POST /api/business-services/v1/{serviceId}:execute</t>
         </is>
       </c>
       <c r="C40" s="4" t="n"/>
@@ -2216,12 +2281,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>권한 판정</t>
+          <t>필수 Header</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>BS_SERVICE_ROLE(화면ID:액션) ∩ 외부 권한API 사용자 화면권한 → AND</t>
+          <t>X-Client-ID(Y), Authorization(Y), Content-Type: application/json (§5.2)</t>
         </is>
       </c>
       <c r="C41" s="4" t="n"/>
@@ -2229,36 +2294,53 @@
       <c r="E41" s="4" t="n"/>
       <c r="F41" s="4" t="n"/>
     </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>권한 판정</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>BS_SERVICE_ROLE(화면ID:액션) ∩ 외부 권한API 사용자 화면권한 → AND</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n"/>
+      <c r="D42" s="4" t="n"/>
+      <c r="E42" s="4" t="n"/>
+      <c r="F42" s="4" t="n"/>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>7. 화면 예시 (샘플 목업 — 문서 기준 재현)</t>
         </is>
       </c>
-      <c r="B43" s="4" t="n"/>
-      <c r="C43" s="4" t="n"/>
-      <c r="D43" s="4" t="n"/>
-      <c r="E43" s="4" t="n"/>
-      <c r="F43" s="4" t="n"/>
+      <c r="B44" s="4" t="n"/>
+      <c r="C44" s="4" t="n"/>
+      <c r="D44" s="4" t="n"/>
+      <c r="E44" s="4" t="n"/>
+      <c r="F44" s="4" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A38:F38"/>
     <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B39:F39"/>
     <mergeCell ref="B6:F6"/>
+    <mergeCell ref="A44:F44"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B28:F28"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="A9:F9"/>
+    <mergeCell ref="B42:F42"/>
     <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A39:F39"/>
     <mergeCell ref="B40:F40"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="B41:F41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/docs/별첨D_화면설계서.xlsx
+++ b/docs/별첨D_화면설계서.xlsx
@@ -7,9 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화면 목록 관리" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CON-01" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CON-02" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개정이력" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화면 목록 관리" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CON-01" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CON-02" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +53,12 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="7">
@@ -113,10 +120,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -130,9 +147,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -562,6 +576,218 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>개정 이력 (Revision History)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>문서: 별첨D 화면 설계서 (IFRS17 Business Service Console)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>버전</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>개정일자</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>개정자</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>변경 내용</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>v1.0</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>DBInc</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>최초 작성 — 설계서 §8 기준 CON-01/CON-02 화면설계서(화면 목록 + 2화면)</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>v1.1</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>DBInc</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>CON-01/CON-02 샘플 화면 목업 이미지 삽입</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>문서 기준 재현</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>v1.2</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>DBInc</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>CON-01 사용 여부를 라디오 컴포넌트(사용/미사용)로 변경</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>v1.3</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>DBInc</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>CON-01 필요 권한 화면ID 예시 반영(ICCOM123:inqy)</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>화면ID:액션 규약</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>DBInc</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>CON-01/CON-02에 저장 위치·유효성·감사로그 매핑 열 추가</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>DBInc</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>개정이력 시트 추가</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -582,243 +808,243 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>문서 근거</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>상세설계서 v1.3 §8 Business Service Console 설계 (§8.1~8.6)</t>
         </is>
       </c>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="8" t="n"/>
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="8" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>대상 시스템</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>IFRS17 Business Service Console (Phase 1)</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="n"/>
-      <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>화면 수</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>2개 (CON-01 서비스 명세 관리, CON-02 서비스 Test)</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="8" t="n"/>
+      <c r="F4" s="8" t="n"/>
+      <c r="G4" s="8" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>■ 화면 목록</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>화면 ID</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>화면명</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>화면 유형</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>주요 기능</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>연계 테이블 / API</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>CON-01</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>서비스 명세 관리</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>관리(등록/수정/조회)</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>서비스 목록 조회, 신규 등록, 상세 조회, 수정, 사용/미사용 설정</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>BS_SERVICE, BS_SERVICE_VERSION, BS_SERVICE_ROLE</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>단일 화면에서 목록+상세영역 구성</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>CON-02</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>서비스 Test</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>실행(테스트)</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>서비스 선택, Request JSON 입력, 실행, Response·오류·처리시간 확인</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>공통 Endpoint POST /api/business-services/v1/{serviceId}:execute</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>실제 공통 Endpoint 사용, Phase1 운영은 READ만</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>■ 개발 범위 / 단순화 원칙 (§8.1)</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>목적</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>WAS에 배포된 Java Business Service 구현체의 명세를 등록·수정·조회하고 공통 Endpoint로 요청/응답을 시험</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>포함</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>서비스 명세 관리(CON-01), 서비스 Test(CON-02), 저장 시 Bean·Interface·ID 자동 검증</t>
         </is>
       </c>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>승인 Workflow, 다단계 Lifecycle, Dashboard, 배포관리, JAR 업로드, 실시간 모니터링, Java 빌드·배포</t>
         </is>
       </c>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -836,7 +1062,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -861,808 +1087,808 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>1. 화면 개요</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="8" t="n"/>
+      <c r="F2" s="8" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>화면 ID</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>CON-01</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="n"/>
-      <c r="F3" s="4" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>화면명</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>서비스 명세 관리</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="8" t="n"/>
+      <c r="F4" s="8" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>목적</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>WAS 배포된 Business Service 구현체의 명세를 등록·수정·조회하고 사용/미사용을 설정</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>운영자 (등록·변경·권한부여는 운영자 역할로 제한, §6.2)</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>화면 구성</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>단일 화면 = [좌] 서비스 목록 영역 + [우] 서비스 명세 등록/수정 영역</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>2. 화면 구성 영역</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>영역</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>구성 요소</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>좌측: 서비스 목록</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>검색창(서비스ID/서비스명), [조회] 버튼, 목록(Service ID·서비스명·사용)</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>검색·조회, 행 선택 시 우측에 상세 로딩, [신규] 버튼으로 신규 등록 시작</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>우측: 명세 등록/수정</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>입력 폼(하단 필드 명세 참조), [저장]·[취소] 버튼</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>신규 등록 / 상세 조회 / 수정 / 사용여부 설정</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>3. 입력 필드 명세 (§8.3) — 저장 위치 및 저장 시 유효성 체크</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>필드명</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>필수</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>컨트롤</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>저장 위치 (테이블.컬럼)</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>저장 시 유효성 체크</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Service ID</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>입력(신규)/읽기전용(수정)</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>BS_SERVICE.service_id</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>정규식 ^[A-Z0-9]+(\.[A-Z0-9]+)+$ (대문자·숫자+점) · 중복 금지(existsById) · Handler.serviceId()와 일치</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>서비스명</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>텍스트</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>BS_SERVICE.service_name</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>필수 · 100자 이내</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>결산 진행상태 조회</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>서비스 설명</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>텍스트</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>BS_SERVICE.service_description</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>필수(§8.3) · varchar(300)</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>결산 단계별 처리상태를 조회한다</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>버전</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>텍스트</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>BS_SERVICE_VERSION.version</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>필수 · 동일 Service ID 내 중복 금지</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Spring Bean</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>텍스트</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>BS_SERVICE_VERSION.implementation_bean</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>필수 · Bean 존재 · BusinessServiceHandler 구현 · Handler.serviceId()=Service ID</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>closingStatusBusinessService</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>요청 JSON 명세</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>텍스트영역</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>BS_SERVICE_VERSION.request_schema</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>JSON 형식·필수값 정의(§8.3)</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F21" s="11" t="inlineStr">
         <is>
           <t>{ closingMonth, closingType }</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>응답 JSON 명세</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>텍스트영역</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>BS_SERVICE_VERSION.response_schema</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>JSON 형식·필드 설명(§8.3)</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>{ stage, status, startTime, endTime }</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>필요 권한</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>텍스트(멀티)</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>BS_SERVICE_ROLE.role_code (행 단위 N개)</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E23" s="11" t="inlineStr">
         <is>
           <t>최소 1개 · 형식 화면ID:액션 = [A-Z]{4}M[0-9]{3}:(inqy|sv|cnfr|aprl|prt)</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>ICCOM123:inqy</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>사용 여부</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>라디오(사용/미사용)</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>BS_SERVICE.active_yn + BS_SERVICE_VERSION.status_code</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>사용→active_yn=Y &amp; status_code=ACTIVE / 미사용→N &amp; INACTIVE · '사용' 저장 시 Bean 재검증</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>유효성 근거</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>저장 검증은 ServiceSpecService(create/update·validateCommon·validateBean, CON-ACC-01)에서 수행. '필요 권한' 형식검증(화면ID:액션)은 확정 규약으로 코드 반영 예정.</t>
         </is>
       </c>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="4" t="n"/>
+      <c r="C25" s="8" t="n"/>
+      <c r="D25" s="8" t="n"/>
+      <c r="E25" s="8" t="n"/>
+      <c r="F25" s="8" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>4. 버튼 / 기능</t>
         </is>
       </c>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="4" t="n"/>
+      <c r="B27" s="8" t="n"/>
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="8" t="n"/>
+      <c r="E27" s="8" t="n"/>
+      <c r="F27" s="8" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>버튼</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>동작</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>처리</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>조회</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>목록 검색</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>검색어(서비스ID/서비스명)로 서비스 목록 조회</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>등록 시작</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>우측 폼 초기화, 신규 서비스 명세 입력</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>저장</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>등록/수정 확정</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Bean 존재·Interface 구현·Service ID/버전 일치 검증 후 저장. 사용=저장 시 Registry 갱신→외부 호출 허용</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>취소</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>입력 취소</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>편집 내용 폐기</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>5. 처리 로직 — 서비스 등록·외부 공개 흐름 (§8.4)</t>
         </is>
       </c>
-      <c r="B34" s="4" t="n"/>
-      <c r="C34" s="4" t="n"/>
-      <c r="D34" s="4" t="n"/>
-      <c r="E34" s="4" t="n"/>
-      <c r="F34" s="4" t="n"/>
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="8" t="n"/>
+      <c r="F34" s="8" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>순서</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>처리</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="10" t="inlineStr">
         <is>
           <t>주체</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>BusinessServiceHandler 구현 클래스 작성·테스트</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>개발자</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>Java 클래스를 IFRS17 WAS에 배포</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>DB-INC</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>관리콘솔에서 서비스 명세 신규 등록</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>운영자</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>Bean 존재·Interface 구현·Service ID/버전 일치 검증</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>시스템</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>서비스 Test 화면에서 요청·응답 확인</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>운영자</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>사용 여부 '사용' 저장 → Registry 갱신, 외부 호출 허용</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>시스템</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>사용 여부 '미사용' 변경 → 즉시 신규 호출 차단</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>시스템</t>
         </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>6. 연계</t>
         </is>
       </c>
-      <c r="B44" s="4" t="n"/>
-      <c r="C44" s="4" t="n"/>
-      <c r="D44" s="4" t="n"/>
-      <c r="E44" s="4" t="n"/>
-      <c r="F44" s="4" t="n"/>
+      <c r="B44" s="8" t="n"/>
+      <c r="C44" s="8" t="n"/>
+      <c r="D44" s="8" t="n"/>
+      <c r="E44" s="8" t="n"/>
+      <c r="F44" s="8" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>연계 테이블</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>BS_SERVICE, BS_SERVICE_VERSION, BS_SERVICE_ROLE (+ BS_CHANGE_HISTORY 변경이력)</t>
         </is>
       </c>
-      <c r="C45" s="4" t="n"/>
-      <c r="D45" s="4" t="n"/>
-      <c r="E45" s="4" t="n"/>
-      <c r="F45" s="4" t="n"/>
+      <c r="C45" s="8" t="n"/>
+      <c r="D45" s="8" t="n"/>
+      <c r="E45" s="8" t="n"/>
+      <c r="F45" s="8" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>검증(CON-ACC-01)</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>Bean 미등록/Interface 미구현/ServiceId 불일치 시 저장·사용전환 차단</t>
         </is>
       </c>
-      <c r="C46" s="4" t="n"/>
-      <c r="D46" s="4" t="n"/>
-      <c r="E46" s="4" t="n"/>
-      <c r="F46" s="4" t="n"/>
+      <c r="C46" s="8" t="n"/>
+      <c r="D46" s="8" t="n"/>
+      <c r="E46" s="8" t="n"/>
+      <c r="F46" s="8" t="n"/>
     </row>
     <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>7. 화면 예시 (샘플 목업 — 문서 기준 재현)</t>
         </is>
       </c>
-      <c r="B48" s="4" t="n"/>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="n"/>
-      <c r="F48" s="4" t="n"/>
+      <c r="B48" s="8" t="n"/>
+      <c r="C48" s="8" t="n"/>
+      <c r="D48" s="8" t="n"/>
+      <c r="E48" s="8" t="n"/>
+      <c r="F48" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -1688,7 +1914,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1713,614 +1939,614 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>1. 화면 개요</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="8" t="n"/>
+      <c r="F2" s="8" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>화면 ID</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>CON-02</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="n"/>
-      <c r="F3" s="4" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>화면명</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>서비스 Test</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="8" t="n"/>
+      <c r="F4" s="8" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>목적</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>등록된 서비스를 공통 Endpoint로 실제 호출하여 요청/응답을 시험</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>운영자</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>중요 원칙</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Test 실행은 운영 호출과 동일 경로(Controller·Dispatcher·권한검사·Handler·감사로그) 사용</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>2. 화면 구성 영역</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>영역</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>구성 요소</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>서비스 선택</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>서비스 목록/선택, 버전(serviceVersion)</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>사용/미사용 서비스 선택 가능 (미배포·Bean 불일치는 실행 불가)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>요청 입력</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>Request JSON 입력창</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>등록된 요청 명세에 따라 형식·필수값 검증</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>실행</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>[실행] 버튼</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>공통 Endpoint 호출</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>응답 출력</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>HTTP 상태 / Response JSON / 오류 / 처리시간</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>결과 표시</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>3. 입력 항목 — 요청 매핑 및 유효성 체크</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>필수</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>컨트롤</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>요청 매핑 (Controller/DTO)</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>유효성 체크</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>서비스 선택</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>목록 선택</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Path {serviceId} → BusinessServiceController.execute</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>사용/미사용 선택 가능하나 미배포·Bean 불일치는 실행 불가(§8.6)</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>IFRS17.CLOSING.STATUS</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>serviceVersion</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>텍스트</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>StandardRequest.serviceVersion</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>미입력 시 최신 ACTIVE 버전 자동 선택</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Request JSON</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>텍스트영역</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>StandardRequest.parameters</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>등록된 요청 명세 기준 형식·필수값 검증 → Handler.validate()(§8.6)</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>{ "parameters": { "closingYearMonth": "2026-06" } }</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>4. 출력 항목 — 표시 및 감사로그 저장 위치 (§8.6)</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>산출 / 저장 위치 (테이블.컬럼)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>HTTP 상태</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>응답 HTTP 상태코드 (예: 200, 400, 403, 500)</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>ResponseEntity status + BS_CALL_LOG.http_status</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Response JSON</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>표준 Response 형식(JSON)</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>StandardResponse (결과 원문 미저장 · parameter_hash만 기록)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>오류코드·오류메시지</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>실패 시 표준 오류코드(부록A: BS-VAL-001 등)와 메시지</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>StandardResponse.error + BS_CALL_LOG.error_code / error_id</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>처리시간</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>서버 처리 소요시간(ms)</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" s="11" t="inlineStr">
         <is>
           <t>StandardResponse.elapsedMs + BS_CALL_LOG.elapsed_ms</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>감사 기록</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>모든 Test 실행은 운영 호출과 동일 경로로 BS_CALL_LOG에 감사 기록됨(request_id·status_code·elapsed_ms 등, §8.6)</t>
         </is>
       </c>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="4" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="8" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>5. 처리 기준 (§8.6)</t>
         </is>
       </c>
-      <c r="B30" s="4" t="n"/>
-      <c r="C30" s="4" t="n"/>
-      <c r="D30" s="4" t="n"/>
-      <c r="E30" s="4" t="n"/>
-      <c r="F30" s="4" t="n"/>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="8" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>기준</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>목록에서 사용/미사용 서비스 선택 가능하나, 미배포·Bean 불일치 서비스는 실행 불가</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>Request JSON은 등록된 요청 명세에 따라 형식·필수값 검증</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Test 실행은 운영 호출과 동일 경로(Controller·Dispatcher·권한검사·Handler·감사로그) 사용</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>화면에 HTTP 상태·표준 Response JSON·오류코드/메시지·처리시간 표시</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>Phase 1 운영환경 Test는 READ 서비스만 허용</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>민감 데이터는 일반 호출과 동일 기준으로 마스킹</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>6. 연계</t>
         </is>
       </c>
-      <c r="B39" s="4" t="n"/>
-      <c r="C39" s="4" t="n"/>
-      <c r="D39" s="4" t="n"/>
-      <c r="E39" s="4" t="n"/>
-      <c r="F39" s="4" t="n"/>
+      <c r="B39" s="8" t="n"/>
+      <c r="C39" s="8" t="n"/>
+      <c r="D39" s="8" t="n"/>
+      <c r="E39" s="8" t="n"/>
+      <c r="F39" s="8" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>공통 Endpoint</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>POST /api/business-services/v1/{serviceId}:execute</t>
         </is>
       </c>
-      <c r="C40" s="4" t="n"/>
-      <c r="D40" s="4" t="n"/>
-      <c r="E40" s="4" t="n"/>
-      <c r="F40" s="4" t="n"/>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="8" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>필수 Header</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>X-Client-ID(Y), Authorization(Y), Content-Type: application/json (§5.2)</t>
         </is>
       </c>
-      <c r="C41" s="4" t="n"/>
-      <c r="D41" s="4" t="n"/>
-      <c r="E41" s="4" t="n"/>
-      <c r="F41" s="4" t="n"/>
+      <c r="C41" s="8" t="n"/>
+      <c r="D41" s="8" t="n"/>
+      <c r="E41" s="8" t="n"/>
+      <c r="F41" s="8" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>권한 판정</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>BS_SERVICE_ROLE(화면ID:액션) ∩ 외부 권한API 사용자 화면권한 → AND</t>
         </is>
       </c>
-      <c r="C42" s="4" t="n"/>
-      <c r="D42" s="4" t="n"/>
-      <c r="E42" s="4" t="n"/>
-      <c r="F42" s="4" t="n"/>
+      <c r="C42" s="8" t="n"/>
+      <c r="D42" s="8" t="n"/>
+      <c r="E42" s="8" t="n"/>
+      <c r="F42" s="8" t="n"/>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>7. 화면 예시 (샘플 목업 — 문서 기준 재현)</t>
         </is>
       </c>
-      <c r="B44" s="4" t="n"/>
-      <c r="C44" s="4" t="n"/>
-      <c r="D44" s="4" t="n"/>
-      <c r="E44" s="4" t="n"/>
-      <c r="F44" s="4" t="n"/>
+      <c r="B44" s="8" t="n"/>
+      <c r="C44" s="8" t="n"/>
+      <c r="D44" s="8" t="n"/>
+      <c r="E44" s="8" t="n"/>
+      <c r="F44" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="17">

--- a/docs/별첨D_화면설계서.xlsx
+++ b/docs/별첨D_화면설계서.xlsx
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>최초 작성 — 설계서 §8 기준 CON-01/CON-02 화면설계서(화면 목록 + 2화면)</t>
+          <t>최초 작성 — 설계서 §8 기준 CON-01/CON-02 화면설계서(3시트). 샘플 화면 목업 이미지, 사용여부 라디오 컴포넌트, 필요권한 화면ID(ICCOM123:inqy), 저장 위치·유효성·감사로그 매핑 열</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr"/>
@@ -668,110 +668,10 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>CON-01/CON-02 샘플 화면 목업 이미지 삽입</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>문서 기준 재현</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>v1.2</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>DBInc</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>CON-01 사용 여부를 라디오 컴포넌트(사용/미사용)로 변경</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>v1.3</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>DBInc</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>CON-01 필요 권한 화면ID 예시 반영(ICCOM123:inqy)</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>화면ID:액션 규약</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>v1.4</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>DBInc</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>CON-01/CON-02에 저장 위치·유효성·감사로그 매핑 열 추가</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>v1.5</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>DBInc</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
           <t>개정이력 시트 추가</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/docs/별첨D_화면설계서.xlsx
+++ b/docs/별첨D_화면설계서.xlsx
@@ -233,10 +233,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>49</row>
+      <row>50</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9334500" cy="5457825"/>
+    <ext cx="9334500" cy="5743575"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -672,6 +672,33 @@
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>v1.2</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>DBInc</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>CON-01에 서비스 유형(service_type) 필드 추가</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>테이블설계서 대조 시 누락 확인 — BS_SERVICE.service_type NOT NULL</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -968,7 +995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1284,7 +1311,7 @@
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>버전</t>
+          <t>서비스 유형</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
@@ -1294,29 +1321,29 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>텍스트</t>
+          <t>라디오(READ/ACTION)</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>BS_SERVICE_VERSION.version</t>
+          <t>BS_SERVICE.service_type</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>필수 · 동일 Service ID 내 중복 금지</t>
+          <t>필수 · READ 또는 ACTION (validateCommon 검증)</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>READ</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Spring Bean</t>
+          <t>버전</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -1331,24 +1358,24 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>BS_SERVICE_VERSION.implementation_bean</t>
+          <t>BS_SERVICE_VERSION.version</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>필수 · Bean 존재 · BusinessServiceHandler 구현 · Handler.serviceId()=Service ID</t>
+          <t>필수 · 동일 Service ID 내 중복 금지</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>closingStatusBusinessService</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>요청 JSON 명세</t>
+          <t>Spring Bean</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
@@ -1358,29 +1385,29 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>텍스트영역</t>
+          <t>텍스트</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>BS_SERVICE_VERSION.request_schema</t>
+          <t>BS_SERVICE_VERSION.implementation_bean</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>JSON 형식·필수값 정의(§8.3)</t>
+          <t>필수 · Bean 존재 · BusinessServiceHandler 구현 · Handler.serviceId()=Service ID</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>{ closingMonth, closingType }</t>
+          <t>closingStatusBusinessService</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>응답 JSON 명세</t>
+          <t>요청 JSON 명세</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -1395,24 +1422,24 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>BS_SERVICE_VERSION.response_schema</t>
+          <t>BS_SERVICE_VERSION.request_schema</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>JSON 형식·필드 설명(§8.3)</t>
+          <t>JSON 형식·필수값 정의(§8.3)</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>{ stage, status, startTime, endTime }</t>
+          <t>{ closingMonth, closingType }</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>필요 권한</t>
+          <t>응답 JSON 명세</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
@@ -1422,341 +1449,357 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>텍스트(멀티)</t>
+          <t>텍스트영역</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>BS_SERVICE_ROLE.role_code (행 단위 N개)</t>
+          <t>BS_SERVICE_VERSION.response_schema</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>최소 1개 · 형식 화면ID:액션 = [A-Z]{4}M[0-9]{3}:(inqy|sv|cnfr|aprl|prt)</t>
+          <t>JSON 형식·필드 설명(§8.3)</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>ICCOM123:inqy</t>
+          <t>{ stage, status, startTime, endTime }</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
+          <t>필요 권한</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>텍스트(멀티)</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>BS_SERVICE_ROLE.role_code (행 단위 N개)</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>최소 1개 · 형식 화면ID:액션 = [A-Z]{4}M[0-9]{3}:(inqy|sv|cnfr|aprl|prt)</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>ICCOM123:inqy</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
           <t>사용 여부</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>라디오(사용/미사용)</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>BS_SERVICE.active_yn + BS_SERVICE_VERSION.status_code</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E25" s="11" t="inlineStr">
         <is>
           <t>사용→active_yn=Y &amp; status_code=ACTIVE / 미사용→N &amp; INACTIVE · '사용' 저장 시 Bean 재검증</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>사용</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>유효성 근거</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>저장 검증은 ServiceSpecService(create/update·validateCommon·validateBean, CON-ACC-01)에서 수행. '필요 권한' 형식검증(화면ID:액션)은 확정 규약으로 코드 반영 예정.</t>
         </is>
       </c>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="8" t="n"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>4. 버튼 / 기능</t>
         </is>
       </c>
-      <c r="B27" s="8" t="n"/>
-      <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
-      <c r="E27" s="8" t="n"/>
-      <c r="F27" s="8" t="n"/>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="B28" s="8" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="8" t="n"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>버튼</t>
         </is>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>동작</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>처리</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>조회</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>목록 검색</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>검색어(서비스ID/서비스명)로 서비스 목록 조회</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>등록 시작</t>
         </is>
       </c>
-      <c r="C30" s="11" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>우측 폼 초기화, 신규 서비스 명세 입력</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>저장</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>등록/수정 확정</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Bean 존재·Interface 구현·Service ID/버전 일치 검증 후 저장. 사용=저장 시 Registry 갱신→외부 호출 허용</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>취소</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>입력 취소</t>
         </is>
       </c>
-      <c r="C32" s="11" t="inlineStr">
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>편집 내용 폐기</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>5. 처리 로직 — 서비스 등록·외부 공개 흐름 (§8.4)</t>
         </is>
       </c>
-      <c r="B34" s="8" t="n"/>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
-      <c r="E34" s="8" t="n"/>
-      <c r="F34" s="8" t="n"/>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="B35" s="8" t="n"/>
+      <c r="C35" s="8" t="n"/>
+      <c r="D35" s="8" t="n"/>
+      <c r="E35" s="8" t="n"/>
+      <c r="F35" s="8" t="n"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>순서</t>
         </is>
       </c>
-      <c r="B35" s="10" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>처리</t>
         </is>
       </c>
-      <c r="C35" s="10" t="inlineStr">
+      <c r="C36" s="10" t="inlineStr">
         <is>
           <t>주체</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>BusinessServiceHandler 구현 클래스 작성·테스트</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>개발자</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>Java 클래스를 IFRS17 WAS에 배포</t>
         </is>
       </c>
-      <c r="C37" s="11" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>DB-INC</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>관리콘솔에서 서비스 명세 신규 등록</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>운영자</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="11" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B39" s="11" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>Bean 존재·Interface 구현·Service ID/버전 일치 검증</t>
         </is>
       </c>
-      <c r="C39" s="11" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>시스템</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>서비스 Test 화면에서 요청·응답 확인</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>운영자</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="11" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B41" s="11" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>사용 여부 '사용' 저장 → Registry 갱신, 외부 호출 허용</t>
         </is>
       </c>
-      <c r="C41" s="11" t="inlineStr">
+      <c r="C42" s="11" t="inlineStr">
         <is>
           <t>시스템</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>사용 여부 '미사용' 변경 → 즉시 신규 호출 차단</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>시스템</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="9" t="inlineStr">
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="9" t="inlineStr">
         <is>
           <t>6. 연계</t>
         </is>
       </c>
-      <c r="B44" s="8" t="n"/>
-      <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="n"/>
-      <c r="E44" s="8" t="n"/>
-      <c r="F44" s="8" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>연계 테이블</t>
-        </is>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>BS_SERVICE, BS_SERVICE_VERSION, BS_SERVICE_ROLE (+ BS_CHANGE_HISTORY 변경이력)</t>
-        </is>
-      </c>
+      <c r="B45" s="8" t="n"/>
       <c r="C45" s="8" t="n"/>
       <c r="D45" s="8" t="n"/>
       <c r="E45" s="8" t="n"/>
@@ -1765,12 +1808,12 @@
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>검증(CON-ACC-01)</t>
+          <t>연계 테이블</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Bean 미등록/Interface 미구현/ServiceId 불일치 시 저장·사용전환 차단</t>
+          <t>BS_SERVICE, BS_SERVICE_VERSION, BS_SERVICE_ROLE (+ BS_CHANGE_HISTORY 변경이력)</t>
         </is>
       </c>
       <c r="C46" s="8" t="n"/>
@@ -1778,36 +1821,52 @@
       <c r="E46" s="8" t="n"/>
       <c r="F46" s="8" t="n"/>
     </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="9" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>검증(CON-ACC-01)</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Bean 미등록/Interface 미구현/ServiceId 불일치 시 저장·사용전환 차단</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="n"/>
+      <c r="D47" s="8" t="n"/>
+      <c r="E47" s="8" t="n"/>
+      <c r="F47" s="8" t="n"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="9" t="inlineStr">
         <is>
           <t>7. 화면 예시 (샘플 목업 — 문서 기준 재현)</t>
         </is>
       </c>
-      <c r="B48" s="8" t="n"/>
-      <c r="C48" s="8" t="n"/>
-      <c r="D48" s="8" t="n"/>
-      <c r="E48" s="8" t="n"/>
-      <c r="F48" s="8" t="n"/>
+      <c r="B49" s="8" t="n"/>
+      <c r="C49" s="8" t="n"/>
+      <c r="D49" s="8" t="n"/>
+      <c r="E49" s="8" t="n"/>
+      <c r="F49" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A49:F49"/>
     <mergeCell ref="B7:F7"/>
+    <mergeCell ref="A28:F28"/>
     <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B47:F47"/>
     <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A44:F44"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="A45:F45"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="B45:F45"/>
-    <mergeCell ref="A34:F34"/>
     <mergeCell ref="B46:F46"/>
-    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="B26:F26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/docs/별첨D_화면설계서.xlsx
+++ b/docs/별첨D_화면설계서.xlsx
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -697,6 +697,33 @@
       <c r="E7" s="5" t="inlineStr">
         <is>
           <t>테이블설계서 대조 시 누락 확인 — BS_SERVICE.service_type NOT NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>v1.3</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>DBInc</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>CON-01 사용 여부 저장 위치를 BS_SERVICE_VERSION.status_code로 한정</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>bs_service.active_yn은 최초 등록 시 Y 고정·미변경</t>
         </is>
       </c>
     </row>
@@ -1518,12 +1545,12 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>BS_SERVICE.active_yn + BS_SERVICE_VERSION.status_code</t>
+          <t>BS_SERVICE_VERSION.status_code</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>사용→active_yn=Y &amp; status_code=ACTIVE / 미사용→N &amp; INACTIVE · '사용' 저장 시 Bean 재검증</t>
+          <t>사용→ACTIVE / 미사용→INACTIVE · '사용' 저장 시 Bean 재검증 (bs_service.active_yn은 최초 등록 시 Y 고정, 미변경)</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">

--- a/docs/별첨D_화면설계서.xlsx
+++ b/docs/별첨D_화면설계서.xlsx
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -726,6 +726,29 @@
           <t>bs_service.active_yn은 최초 등록 시 Y 고정·미변경</t>
         </is>
       </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>DBInc</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>CON-01 저장 처리 설명 보강(버전 확인 후 UPDATE/INSERT)</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1651,7 +1674,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Bean 존재·Interface 구현·Service ID/버전 일치 검증 후 저장. 사용=저장 시 Registry 갱신→외부 호출 허용</t>
+          <t>Bean·Interface·Service ID 검증 후 저장. 버전 변경 시: 해당 버전이 있으면 UPDATE, 없으면 신규 버전 INSERT. 사용=저장 시 Registry 갱신→외부 호출 허용</t>
         </is>
       </c>
     </row>

--- a/docs/별첨D_화면설계서.xlsx
+++ b/docs/별첨D_화면설계서.xlsx
@@ -745,7 +745,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>CON-01 저장 처리 설명 보강(버전 확인 후 UPDATE/INSERT)</t>
+          <t>CON-01 저장 처리 설명 보강(버전 확인 후 UPDATE/INSERT, 기존 버전 자동 비활성화 없음 명시)</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr"/>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Bean·Interface·Service ID 검증 후 저장. 버전 변경 시: 해당 버전이 있으면 UPDATE, 없으면 신규 버전 INSERT. 사용=저장 시 Registry 갱신→외부 호출 허용</t>
+          <t>Bean·Interface·Service ID 검증 후 저장. 버전 변경 시: 해당 버전이 있으면 UPDATE, 없으면 신규 버전 INSERT (신규 버전 INSERT 시 기존 버전은 자동 비활성화되지 않음·수동 관리). 사용=저장 시 Registry 갱신→외부 호출 허용</t>
         </is>
       </c>
     </row>
